--- a/sheets/조재수대금교본/검수/산조기본3.xlsx
+++ b/sheets/조재수대금교본/검수/산조기본3.xlsx
@@ -4326,37 +4326,33 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∼
-‹</t>
+          <t xml:space="preserve">太∼</t>
         </is>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∼
-‹</t>
+          <t xml:space="preserve">太∼</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-南ㄴ
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南c
-林
-‹</t>
+          <t xml:space="preserve">南
+林</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -4368,7 +4364,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -4380,13 +4376,13 @@
       <c r="Q3" s="22"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㅋ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="U3" s="22"/>
@@ -4405,23 +4401,11 @@
         </is>
       </c>
       <c r="E4" s="23"/>
-      <c r="F4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zㅎ</t>
-        </is>
-      </c>
+      <c r="F4" s="24"/>
       <c r="G4" s="25"/>
-      <c r="H4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zㅎ</t>
-        </is>
-      </c>
+      <c r="H4" s="24"/>
       <c r="I4" s="25"/>
-      <c r="J4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zㅎ</t>
-        </is>
-      </c>
+      <c r="J4" s="24"/>
       <c r="K4" s="25"/>
       <c r="L4" s="21"/>
       <c r="M4" s="23"/>
@@ -4429,11 +4413,7 @@
       <c r="O4" s="23"/>
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
-      <c r="R4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R4" s="21"/>
       <c r="S4" s="23"/>
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
@@ -4442,68 +4422,41 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="E5" s="26"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="G5" s="26"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="26"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="26"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="26"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="26"/>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P5" s="21"/>
       <c r="Q5" s="26"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∼
-‹</t>
+          <t xml:space="preserve">汰∼</t>
         </is>
       </c>
       <c r="S5" s="26"/>
       <c r="T5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ
-ﾉ
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="U5" s="26"/>
@@ -4524,42 +4477,39 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕c
+          <t xml:space="preserve">潕
 淋</t>
         </is>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∼
-‹</t>
+          <t xml:space="preserve">太∼</t>
         </is>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ·</t>
+          <t xml:space="preserve">南·</t>
         </is>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ·</t>
+          <t xml:space="preserve">湳·</t>
         </is>
       </c>
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ㄴ南潢
-南
-ﾉ
-‹</t>
+          <t xml:space="preserve">南潢
+南</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -4580,21 +4530,17 @@
       <c r="A7" s="0"/>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅎ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C7" s="25"/>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅎ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="E7" s="25"/>
-      <c r="F7" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zㅎ</t>
-        </is>
-      </c>
+      <c r="F7" s="24"/>
       <c r="G7" s="25"/>
       <c r="H7" s="21"/>
       <c r="I7" s="23"/>
@@ -4627,70 +4573,39 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="G8" s="26"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="26"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="26"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="O8" s="26"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="26"/>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R8" s="21"/>
       <c r="S8" s="26"/>
-      <c r="T8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T8" s="21"/>
       <c r="U8" s="26"/>
     </row>
     <row r="9" ht="145.5" customHeight="true">
@@ -4704,30 +4619,28 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c㳞汰c
-潢
-ﾉ‹</t>
+          <t xml:space="preserve">㳞汰
+潢</t>
         </is>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕c
-潕c
-‹</t>
+          <t xml:space="preserve">潕
+潕</t>
         </is>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-南ㄴ</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南c
+          <t xml:space="preserve">南
 林</t>
         </is>
       </c>
@@ -4746,7 +4659,7 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
@@ -4770,74 +4683,53 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-ﾉ
 △</t>
         </is>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∼
-‹</t>
+          <t xml:space="preserve">湳∼</t>
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zㅎ</t>
-        </is>
-      </c>
+      <c r="H10" s="24"/>
       <c r="I10" s="25"/>
-      <c r="J10" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zㅎ</t>
-        </is>
-      </c>
+      <c r="J10" s="24"/>
       <c r="K10" s="25"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰c
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="M10" s="23"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="23"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南∼
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="S10" s="23"/>
       <c r="T10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南∼
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="U10" s="23"/>
     </row>
     <row r="11" ht="145.5" customHeight="true">
       <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="26"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∼
-‹</t>
+          <t xml:space="preserve">太∼</t>
         </is>
       </c>
       <c r="E11" s="26"/>
@@ -4847,51 +4739,33 @@
         </is>
       </c>
       <c r="G11" s="26"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="H11" s="21"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J11" s="21"/>
       <c r="K11" s="26"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="M11" s="26"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∼
-‹</t>
+          <t xml:space="preserve">湳∼</t>
         </is>
       </c>
       <c r="O11" s="26"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="P11" s="21"/>
       <c r="Q11" s="26"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∼
-‹</t>
+          <t xml:space="preserve">太∼</t>
         </is>
       </c>
       <c r="S11" s="26"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∼
-‹</t>
+          <t xml:space="preserve">太∼</t>
         </is>
       </c>
       <c r="U11" s="26"/>
@@ -4900,7 +4774,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ·ㅂ</t>
+          <t xml:space="preserve">淋·</t>
         </is>
       </c>
       <c r="C12" s="22"/>
@@ -4936,15 +4810,13 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ
-ﾉ
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -4971,11 +4843,7 @@
         </is>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zㅎ</t>
-        </is>
-      </c>
+      <c r="F13" s="24"/>
       <c r="G13" s="25"/>
       <c r="H13" s="21"/>
       <c r="I13" s="23"/>
@@ -5014,52 +4882,23 @@
       <c r="E14" s="26"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="G14" s="26"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="26"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="26"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="26"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="26"/>
-      <c r="R14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R14" s="21"/>
       <c r="S14" s="26"/>
-      <c r="T14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T14" s="21"/>
       <c r="U14" s="26"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/산조기본3.xlsx
+++ b/sheets/조재수대금교본/검수/산조기본3.xlsx
@@ -4338,20 +4338,20 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㅋ</t>
         </is>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-南</t>
+          <t xml:space="preserve">汰c
+南ㄴ</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南c
 林</t>
         </is>
       </c>
@@ -4364,7 +4364,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㅋ</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -4376,13 +4376,13 @@
       <c r="Q3" s="22"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㅋ</t>
         </is>
       </c>
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㅋ</t>
         </is>
       </c>
       <c r="U3" s="22"/>
@@ -4401,11 +4401,23 @@
         </is>
       </c>
       <c r="E4" s="23"/>
-      <c r="F4" s="24"/>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="24"/>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I4" s="25"/>
-      <c r="J4" s="24"/>
+      <c r="J4" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K4" s="25"/>
       <c r="L4" s="21"/>
       <c r="M4" s="23"/>
@@ -4438,7 +4450,11 @@
         </is>
       </c>
       <c r="G5" s="26"/>
-      <c r="H5" s="21"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="I5" s="26"/>
       <c r="J5" s="21"/>
       <c r="K5" s="26"/>
@@ -4456,7 +4472,8 @@
       <c r="S5" s="26"/>
       <c r="T5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄴ
+ﾉ</t>
         </is>
       </c>
       <c r="U5" s="26"/>
@@ -4477,14 +4494,14 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕
+          <t xml:space="preserve">潕c
 淋</t>
         </is>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄴ</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -4496,20 +4513,21 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南·</t>
+          <t xml:space="preserve">南ㄴ·</t>
         </is>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳·</t>
+          <t xml:space="preserve">湳ㄴ·</t>
         </is>
       </c>
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南潢
-南</t>
+          <t xml:space="preserve">ㄴ南潢
+南
+ﾉ</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -4540,7 +4558,11 @@
         </is>
       </c>
       <c r="E7" s="25"/>
-      <c r="F7" s="24"/>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G7" s="25"/>
       <c r="H7" s="21"/>
       <c r="I7" s="23"/>
@@ -4589,11 +4611,20 @@
         </is>
       </c>
       <c r="G8" s="26"/>
-      <c r="H8" s="21"/>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="I8" s="26"/>
       <c r="J8" s="21"/>
       <c r="K8" s="26"/>
-      <c r="L8" s="21"/>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+ﾉ</t>
+        </is>
+      </c>
       <c r="M8" s="26"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
@@ -4619,28 +4650,29 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰
-潢</t>
+          <t xml:space="preserve">c㳞汰c
+潢
+ﾉ</t>
         </is>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕
-潕</t>
+          <t xml:space="preserve">潕c
+潕c</t>
         </is>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-南</t>
+          <t xml:space="preserve">汰c
+南ㄴ</t>
         </is>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南c
 林</t>
         </is>
       </c>
@@ -4659,7 +4691,7 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄴ</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
@@ -4683,6 +4715,7 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+ﾉ
 △</t>
         </is>
       </c>
@@ -4693,14 +4726,22 @@
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="24"/>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I10" s="25"/>
-      <c r="J10" s="24"/>
+      <c r="J10" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K10" s="25"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+汰c</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -4711,21 +4752,25 @@
       <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南∼
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="S10" s="23"/>
       <c r="T10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南∼
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="U10" s="23"/>
     </row>
     <row r="11" ht="145.5" customHeight="true">
       <c r="A11" s="0"/>
-      <c r="B11" s="21"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C11" s="26"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
@@ -4739,7 +4784,11 @@
         </is>
       </c>
       <c r="G11" s="26"/>
-      <c r="H11" s="21"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="I11" s="26"/>
       <c r="J11" s="21"/>
       <c r="K11" s="26"/>
@@ -4755,7 +4804,11 @@
         </is>
       </c>
       <c r="O11" s="26"/>
-      <c r="P11" s="21"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="Q11" s="26"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
@@ -4774,7 +4827,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋·</t>
+          <t xml:space="preserve">淋ㅋ·ㅂ</t>
         </is>
       </c>
       <c r="C12" s="22"/>
@@ -4810,13 +4863,14 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㅋ</t>
         </is>
       </c>
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄴ
+ﾉ</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -4843,7 +4897,11 @@
         </is>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="24"/>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G13" s="25"/>
       <c r="H13" s="21"/>
       <c r="I13" s="23"/>

--- a/sheets/조재수대금교본/검수/산조기본3.xlsx
+++ b/sheets/조재수대금교본/검수/산조기본3.xlsx
@@ -4270,32 +4270,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="18.03" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="97.56" customHeight="true">
+    <row r="2" ht="114.29" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="145.5" customHeight="true">
+    <row r="3" ht="170.53" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="145.5" customHeight="true">
+    <row r="4" ht="170.53" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="145.5" customHeight="true">
+    <row r="5" ht="170.53" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="U5" s="26"/>
     </row>
-    <row r="6" ht="145.5" customHeight="true">
+    <row r="6" ht="170.53" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="145.5" customHeight="true">
+    <row r="7" ht="170.53" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="24" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="145.5" customHeight="true">
+    <row r="8" ht="170.53" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="26"/>
     </row>
-    <row r="9" ht="145.5" customHeight="true">
+    <row r="9" ht="170.53" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="145.5" customHeight="true">
+    <row r="10" ht="170.53" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="145.5" customHeight="true">
+    <row r="11" ht="170.53" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="U11" s="26"/>
     </row>
-    <row r="12" ht="145.5" customHeight="true">
+    <row r="12" ht="170.53" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="145.5" customHeight="true">
+    <row r="13" ht="170.53" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4922,7 +4922,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="145.5" customHeight="true">
+    <row r="14" ht="170.53" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4965,6 +4965,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="41"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="35"/>
 </worksheet>
 </file>